--- a/数据表/Datas/__tables__.xlsx
+++ b/数据表/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="106">
   <si>
     <t>##var</t>
   </si>
@@ -66,6 +66,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>全名</t>
     </r>
     <r>
@@ -97,10 +103,24 @@
     </r>
   </si>
   <si>
-    <t>记录类名</t>
-  </si>
-  <si>
-    <r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>记录类名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>从</t>
     </r>
     <r>
@@ -123,10 +143,24 @@
     </r>
   </si>
   <si>
-    <t>文件列表</t>
-  </si>
-  <si>
-    <r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>文件列表</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>表</t>
     </r>
     <r>
@@ -149,13 +183,37 @@
     </r>
   </si>
   <si>
-    <t>模式</t>
-  </si>
-  <si>
-    <t>分组</t>
-  </si>
-  <si>
-    <t>注释</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>模式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分组</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>注释</t>
+    </r>
   </si>
   <si>
     <t>输出文件名</t>
@@ -175,16 +233,38 @@
     </r>
   </si>
   <si>
-    <t>多个文件以逗号分隔</t>
-  </si>
-  <si>
-    <t>为空时使用第一个字段</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>多个文件以逗号分隔</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>为空时使用第一个字段</t>
+    </r>
   </si>
   <si>
     <t>one|map|list</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>当前仅客户端</t>
     </r>
     <r>
@@ -236,7 +316,15 @@
     <t>c</t>
   </si>
   <si>
-    <t>全局零散配置（单例）</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>全局零散配置（单例）</t>
+    </r>
   </si>
   <si>
     <t>TbFormatText</t>
@@ -300,7 +388,15 @@
     </r>
   </si>
   <si>
-    <t>稀有度搜索时间</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>稀有度搜索时间</t>
+    </r>
   </si>
   <si>
     <t>TbDifficultyConfig</t>
@@ -332,7 +428,15 @@
     </r>
   </si>
   <si>
-    <t>难度与怪物池</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>难度与怪物池</t>
+    </r>
   </si>
   <si>
     <t>TbCharacterConfig</t>
@@ -364,7 +468,15 @@
     </r>
   </si>
   <si>
-    <t>玩家角色</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>玩家角色</t>
+    </r>
   </si>
   <si>
     <t>TbBattleActionConfig</t>
@@ -396,7 +508,15 @@
     </r>
   </si>
   <si>
-    <t>普通攻击、技能和敌人行动</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>普通攻击、技能和敌人行动</t>
+    </r>
   </si>
   <si>
     <t>TbThreatLevelConfig</t>
@@ -428,7 +548,15 @@
     </r>
   </si>
   <si>
-    <t>警惕与视野参数</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>警惕与视野参数</t>
+    </r>
   </si>
   <si>
     <t>TbEnemyConfig</t>
@@ -460,7 +588,15 @@
     </r>
   </si>
   <si>
-    <t>敌人属性与行为</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人属性与行为</t>
+    </r>
   </si>
   <si>
     <t>TbEnemyPartyConfig</t>
@@ -492,7 +628,15 @@
     </r>
   </si>
   <si>
-    <t>地图敌人对应的战斗队伍</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>地图敌人对应的战斗队伍</t>
+    </r>
   </si>
   <si>
     <t>TbItemConfig</t>
@@ -524,7 +668,15 @@
     </r>
   </si>
   <si>
-    <t>战利品、装备与消耗品</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战利品、装备与消耗品</t>
+    </r>
   </si>
   <si>
     <t>TbResourcePointConfig</t>
@@ -556,7 +708,15 @@
     </r>
   </si>
   <si>
-    <t>五种物资点刷新规则</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>五种物资点刷新规则</t>
+    </r>
   </si>
   <si>
     <t>TbEnemyDropConfig</t>
@@ -588,7 +748,15 @@
     </r>
   </si>
   <si>
-    <t>敌人独立掉落表</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人独立掉落表</t>
+    </r>
   </si>
   <si>
     <t>TbEntityConfig</t>
@@ -603,6 +771,7 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF000000"/>
         <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
@@ -611,6 +780,7 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF000000"/>
         <rFont val="Andale Mono"/>
         <charset val="134"/>
       </rPr>
@@ -618,7 +788,14 @@
     </r>
   </si>
   <si>
-    <t>实体配置</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>实体配置</t>
+    </r>
   </si>
   <si>
     <t>TbMusicConfig</t>
@@ -633,6 +810,7 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF000000"/>
         <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
@@ -641,6 +819,7 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF000000"/>
         <rFont val="Andale Mono"/>
         <charset val="134"/>
       </rPr>
@@ -648,7 +827,14 @@
     </r>
   </si>
   <si>
-    <t>音乐配置</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>音乐配置</t>
+    </r>
   </si>
   <si>
     <t>TbSceneConfig</t>
@@ -663,6 +849,7 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF000000"/>
         <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
@@ -671,6 +858,7 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF000000"/>
         <rFont val="Andale Mono"/>
         <charset val="134"/>
       </rPr>
@@ -678,7 +866,14 @@
     </r>
   </si>
   <si>
-    <t>场景配置</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>场景配置</t>
+    </r>
   </si>
   <si>
     <t>TbSoundConfig</t>
@@ -693,6 +888,7 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF000000"/>
         <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
@@ -701,6 +897,7 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF000000"/>
         <rFont val="Andale Mono"/>
         <charset val="134"/>
       </rPr>
@@ -708,7 +905,14 @@
     </r>
   </si>
   <si>
-    <t>声音配置</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>声音配置</t>
+    </r>
   </si>
   <si>
     <t>TbUIFormConfig</t>
@@ -723,6 +927,7 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF000000"/>
         <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
@@ -731,6 +936,7 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF000000"/>
         <rFont val="Andale Mono"/>
         <charset val="134"/>
       </rPr>
@@ -738,7 +944,14 @@
     </r>
   </si>
   <si>
-    <t>界面配置</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>界面配置</t>
+    </r>
   </si>
   <si>
     <t>TbUISoundConfig</t>
@@ -753,6 +966,7 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF000000"/>
         <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
@@ -761,6 +975,7 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF000000"/>
         <rFont val="Andale Mono"/>
         <charset val="134"/>
       </rPr>
@@ -768,7 +983,57 @@
     </r>
   </si>
   <si>
-    <t>界面音效配置</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>界面音效配置</t>
+    </r>
+  </si>
+  <si>
+    <t>TbSpriteConfig</t>
+  </si>
+  <si>
+    <t>SpriteConfig</t>
+  </si>
+  <si>
+    <r>
+      <t>SpriteConfig_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>图片资源</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.xlsx</t>
+    </r>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>图片资源配置</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -781,7 +1046,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -814,17 +1079,6 @@
       <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="Andale Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
     <font>
@@ -948,6 +1202,29 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202020"/>
+      <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Andale Mono"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1298,22 +1575,31 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1322,151 +1608,149 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1938,7 +2222,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -1946,566 +2230,666 @@
     <col min="3" max="3" width="22" style="1" customWidth="1"/>
     <col min="4" max="4" width="25" style="1" customWidth="1"/>
     <col min="5" max="5" width="38.4705882352941" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6029411764706" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14" style="2" customWidth="1"/>
+    <col min="8" max="8" width="10" style="2" customWidth="1"/>
     <col min="9" max="9" width="14" style="1" customWidth="1"/>
     <col min="10" max="11" width="10" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:11">
-      <c r="A1" s="2" t="s">
+    <row r="1" customHeight="1" spans="1:12">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="1:11">
-      <c r="A2" s="3" t="s">
+    <row r="2" customHeight="1" spans="1:12">
+      <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="4" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:11">
-      <c r="A3" s="3" t="s">
+    <row r="3" customHeight="1" spans="1:12">
+      <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="4" t="s">
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="1:11">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5" t="s">
+    <row r="4" customHeight="1" spans="1:12">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="5" t="b">
+      <c r="D4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5" t="s">
+      <c r="F4" s="9"/>
+      <c r="G4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
     </row>
-    <row r="5" customHeight="1" spans="1:11">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5" t="s">
+    <row r="5" customHeight="1" spans="1:12">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="5" t="b">
+      <c r="D5" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5" t="s">
+      <c r="F5" s="9"/>
+      <c r="G5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
     </row>
-    <row r="6" customHeight="1" spans="1:11">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5" t="s">
+    <row r="6" customHeight="1" spans="1:12">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="5" t="b">
+      <c r="D6" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5" t="s">
+      <c r="F6" s="9"/>
+      <c r="G6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
     </row>
-    <row r="7" customHeight="1" spans="1:11">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5" t="s">
+    <row r="7" customHeight="1" spans="1:12">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="5" t="b">
+      <c r="D7" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5" t="s">
+      <c r="F7" s="9"/>
+      <c r="G7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
     </row>
-    <row r="8" customHeight="1" spans="1:11">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5" t="s">
+    <row r="8" customHeight="1" spans="1:12">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="5" t="b">
+      <c r="D8" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5" t="s">
+      <c r="F8" s="9"/>
+      <c r="G8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
     </row>
-    <row r="9" customHeight="1" spans="1:11">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5" t="s">
+    <row r="9" customHeight="1" spans="1:12">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="5" t="b">
+      <c r="D9" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
+      <c r="F9" s="9"/>
+      <c r="G9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
     </row>
-    <row r="10" customHeight="1" spans="1:11">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5" t="s">
+    <row r="10" customHeight="1" spans="1:12">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="5" t="b">
+      <c r="D10" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5" t="s">
+      <c r="F10" s="9"/>
+      <c r="G10" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
     </row>
-    <row r="11" customHeight="1" spans="1:11">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5" t="s">
+    <row r="11" customHeight="1" spans="1:12">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="5" t="b">
+      <c r="D11" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5" t="s">
+      <c r="F11" s="9"/>
+      <c r="G11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
     </row>
-    <row r="12" customHeight="1" spans="1:11">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5" t="s">
+    <row r="12" customHeight="1" spans="1:12">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="5" t="b">
+      <c r="D12" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5" t="s">
+      <c r="F12" s="9"/>
+      <c r="G12" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
     </row>
-    <row r="13" customHeight="1" spans="1:11">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5" t="s">
+    <row r="13" customHeight="1" spans="1:12">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="5" t="b">
+      <c r="D13" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5" t="s">
+      <c r="F13" s="9"/>
+      <c r="G13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
     </row>
-    <row r="14" customHeight="1" spans="1:11">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5" t="s">
+    <row r="14" customHeight="1" spans="1:12">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D14" s="5" t="b">
+      <c r="D14" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5" t="s">
+      <c r="F14" s="9"/>
+      <c r="G14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
     </row>
-    <row r="15" customHeight="1" spans="1:11">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5" t="s">
+    <row r="15" customHeight="1" spans="1:12">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="5" t="b">
+      <c r="D15" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5" t="s">
+      <c r="F15" s="9"/>
+      <c r="G15" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
     </row>
-    <row r="16" customHeight="1" spans="1:11">
-      <c r="B16" s="7" t="s">
+    <row r="16" customHeight="1" spans="1:12">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="1" t="b">
+      <c r="D16" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="F16" s="9"/>
+      <c r="G16" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>80</v>
       </c>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
     </row>
-    <row r="17" customHeight="1" spans="2:9">
-      <c r="B17" s="7" t="s">
+    <row r="17" customHeight="1" spans="1:12">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="1" t="b">
+      <c r="D17" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="F17" s="9"/>
+      <c r="G17" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>84</v>
       </c>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
     </row>
-    <row r="18" customHeight="1" spans="2:9">
-      <c r="B18" s="7" t="s">
+    <row r="18" customHeight="1" spans="1:12">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="1" t="b">
+      <c r="D18" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="F18" s="9"/>
+      <c r="G18" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="8" t="s">
         <v>88</v>
       </c>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
     </row>
-    <row r="19" customHeight="1" spans="2:9">
-      <c r="B19" s="7" t="s">
+    <row r="19" customHeight="1" spans="1:12">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="1" t="b">
+      <c r="D19" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="F19" s="9"/>
+      <c r="G19" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="H19" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>92</v>
       </c>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
     </row>
-    <row r="20" customHeight="1" spans="2:9">
-      <c r="B20" s="7" t="s">
+    <row r="20" customHeight="1" spans="1:12">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="1" t="b">
+      <c r="D20" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="F20" s="9"/>
+      <c r="G20" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="8" t="s">
         <v>96</v>
       </c>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
     </row>
-    <row r="21" customHeight="1" spans="2:9">
-      <c r="B21" s="7" t="s">
+    <row r="21" customHeight="1" spans="1:12">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D21" s="1" t="b">
+      <c r="D21" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="F21" s="9"/>
+      <c r="G21" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="9" t="s">
         <v>31</v>
       </c>
       <c r="I21" s="8" t="s">
         <v>100</v>
       </c>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:12">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:12">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:12">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/数据表/Datas/__tables__.xlsx
+++ b/数据表/Datas/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16080"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -220,6 +220,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>true</t>
     </r>
     <r>
@@ -288,6 +294,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>GlobalConfig_</t>
     </r>
     <r>
@@ -334,6 +346,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>FormatText_</t>
     </r>
     <r>
@@ -366,6 +384,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>RarityConfig_</t>
     </r>
     <r>
@@ -406,6 +430,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>DifficultyConfig_</t>
     </r>
     <r>
@@ -446,6 +476,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>CharacterConfig_</t>
     </r>
     <r>
@@ -486,6 +522,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>BattleActionConfig_</t>
     </r>
     <r>
@@ -526,6 +568,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>ThreatLevelConfig_</t>
     </r>
     <r>
@@ -566,6 +614,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>EnemyConfig_</t>
     </r>
     <r>
@@ -606,6 +660,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>EnemyPartyConfig_</t>
     </r>
     <r>
@@ -646,6 +706,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>ItemConfig_</t>
     </r>
     <r>
@@ -686,6 +752,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>ResourcePointConfig_</t>
     </r>
     <r>
@@ -726,6 +798,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>EnemyDropConfig_</t>
     </r>
     <r>
@@ -766,6 +844,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>EntityConfig_</t>
     </r>
     <r>
@@ -805,6 +889,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>MusicConfig_</t>
     </r>
     <r>
@@ -844,6 +934,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>SceneConfig_</t>
     </r>
     <r>
@@ -883,6 +979,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>SoundConfig_</t>
     </r>
     <r>
@@ -922,6 +1024,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>UIFormConfig_</t>
     </r>
     <r>
@@ -961,6 +1069,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>UISoundConfig_</t>
     </r>
     <r>
@@ -1000,6 +1114,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>SpriteConfig_</t>
     </r>
     <r>
@@ -1206,12 +1326,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
@@ -1225,6 +1339,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Andale Mono"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202020"/>
+      <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1575,7 +1695,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2230,7 +2350,7 @@
     <col min="3" max="3" width="22" style="1" customWidth="1"/>
     <col min="4" max="4" width="25" style="1" customWidth="1"/>
     <col min="5" max="5" width="38.4705882352941" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6029411764706" style="2" customWidth="1"/>
+    <col min="6" max="6" width="21.3161764705882" style="2" customWidth="1"/>
     <col min="7" max="7" width="14" style="2" customWidth="1"/>
     <col min="8" max="8" width="10" style="2" customWidth="1"/>
     <col min="9" max="9" width="14" style="1" customWidth="1"/>
